--- a/machine_log.xlsx
+++ b/machine_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,132 +486,6 @@
         <is>
           <t>Edit Count</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Loom-02-Updated</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Warp Break Fixed</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Knotting Done</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>John Smith</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-06-20 10:05</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-06-20 10:45</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-06-20 10:31:00</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Running</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Needle</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Supervised</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Loom 3</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Electrical Fault</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Check Electrical Connections/Reset</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Hooria</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-06-19 15:26</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-06-20 15:56</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1470</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-06-20 15:58:02</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Drop Wire</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>inspect the connections</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
